--- a/Data/National Accounts/PSA-20HHSW_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-20HHSW_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE37718-E3E3-46F8-B6FE-3AF261E7024A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7280021-58F7-4B6A-9806-AA1FBCB76304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HHSW" sheetId="14" r:id="rId1"/>
@@ -616,9 +616,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -626,6 +623,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -23643,7 +23643,7 @@
     </row>
     <row r="3" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -23656,7 +23656,7 @@
     </row>
     <row r="6" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -23913,10 +23913,10 @@
         <v>148785.70788018912</v>
       </c>
       <c r="Z12" s="10">
-        <v>172099.96413339669</v>
+        <v>172005.47683909192</v>
       </c>
       <c r="AA12" s="10">
-        <v>199823.8255746442</v>
+        <v>198875.85591211985</v>
       </c>
       <c r="AB12" s="11"/>
       <c r="AC12" s="11"/>
@@ -24065,10 +24065,10 @@
         <v>282974.08159853669</v>
       </c>
       <c r="Z13" s="10">
-        <v>324512.58839263412</v>
+        <v>325102.02705755632</v>
       </c>
       <c r="AA13" s="10">
-        <v>376464.78472241724</v>
+        <v>377997.44987750205</v>
       </c>
       <c r="AB13" s="11"/>
       <c r="AC13" s="11"/>
@@ -24217,10 +24217,10 @@
         <v>28136.084763259329</v>
       </c>
       <c r="Z14" s="10">
-        <v>31672.464315104047</v>
+        <v>30684.186169462639</v>
       </c>
       <c r="AA14" s="10">
-        <v>34497.713064807976</v>
+        <v>33425.097993070594</v>
       </c>
       <c r="AB14" s="11"/>
       <c r="AC14" s="11"/>
@@ -24467,10 +24467,10 @@
         <v>459895.87424198515</v>
       </c>
       <c r="Z16" s="15">
-        <v>528285.01684113487</v>
+        <v>527791.69006611092</v>
       </c>
       <c r="AA16" s="15">
-        <v>610786.32336186944</v>
+        <v>610298.40378269251</v>
       </c>
       <c r="AB16" s="11"/>
       <c r="AC16" s="11"/>
@@ -24862,7 +24862,7 @@
     </row>
     <row r="23" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -24953,7 +24953,7 @@
     </row>
     <row r="26" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -25262,10 +25262,10 @@
         <v>126475.2679437249</v>
       </c>
       <c r="Z32" s="10">
-        <v>140444.48264015571</v>
+        <v>140314.94121838131</v>
       </c>
       <c r="AA32" s="10">
-        <v>155520.8855450229</v>
+        <v>154799.80871523297</v>
       </c>
       <c r="AB32" s="11"/>
       <c r="AC32" s="11"/>
@@ -25414,10 +25414,10 @@
         <v>241174.52130527215</v>
       </c>
       <c r="Z33" s="10">
-        <v>268036.67233009666</v>
+        <v>268509.35254541755</v>
       </c>
       <c r="AA33" s="10">
-        <v>302192.93689616158</v>
+        <v>303329.32526668225</v>
       </c>
       <c r="AB33" s="11"/>
       <c r="AC33" s="11"/>
@@ -25566,10 +25566,10 @@
         <v>22859.857467594808</v>
       </c>
       <c r="Z34" s="10">
-        <v>24699.621336812539</v>
+        <v>23931.472088487324</v>
       </c>
       <c r="AA34" s="10">
-        <v>25806.004147873085</v>
+        <v>25005.756236044097</v>
       </c>
       <c r="AB34" s="11"/>
       <c r="AC34" s="11"/>
@@ -25816,10 +25816,10 @@
         <v>390509.64671659184</v>
       </c>
       <c r="Z36" s="15">
-        <v>433180.77630706492</v>
+        <v>432755.76585228625</v>
       </c>
       <c r="AA36" s="15">
-        <v>483519.82658905757</v>
+        <v>483134.8902179593</v>
       </c>
       <c r="AB36" s="11"/>
       <c r="AC36" s="11"/>
@@ -26211,7 +26211,7 @@
     </row>
     <row r="43" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -26302,7 +26302,7 @@
     </row>
     <row r="46" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -26499,7 +26499,7 @@
         <v>47</v>
       </c>
       <c r="Z50" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA50" s="19"/>
     </row>
@@ -26606,10 +26606,10 @@
         <v>9.7522609524853152</v>
       </c>
       <c r="Y52" s="20">
-        <v>15.669688026743515</v>
+        <v>15.606182401337037</v>
       </c>
       <c r="Z52" s="20">
-        <v>16.10916166127636</v>
+        <v>15.621815983315869</v>
       </c>
       <c r="AA52" s="20"/>
       <c r="AB52" s="11"/>
@@ -26751,10 +26751,10 @@
         <v>13.187214157219799</v>
       </c>
       <c r="Y53" s="20">
-        <v>14.679261987332552</v>
+        <v>14.887563278246716</v>
       </c>
       <c r="Z53" s="20">
-        <v>16.009300775390912</v>
+        <v>16.270406954608461</v>
       </c>
       <c r="AA53" s="20"/>
       <c r="AB53" s="11"/>
@@ -26896,10 +26896,10 @@
         <v>8.1892026563660494</v>
       </c>
       <c r="Y54" s="20">
-        <v>12.568840269000731</v>
+        <v>9.0563467790325802</v>
       </c>
       <c r="Z54" s="20">
-        <v>8.9202050134021817</v>
+        <v>8.9326528279761135</v>
       </c>
       <c r="AA54" s="20"/>
       <c r="AB54" s="11"/>
@@ -27134,10 +27134,10 @@
         <v>11.739999939102262</v>
       </c>
       <c r="Y56" s="20">
-        <v>14.870571020423014</v>
+        <v>14.763301787830514</v>
       </c>
       <c r="Z56" s="20">
-        <v>15.616817416865004</v>
+        <v>15.632438946935068</v>
       </c>
       <c r="AA56" s="20"/>
       <c r="AB56" s="11"/>
@@ -27515,7 +27515,7 @@
     </row>
     <row r="63" spans="1:91" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -27606,7 +27606,7 @@
     </row>
     <row r="66" spans="1:92" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -27803,7 +27803,7 @@
         <v>47</v>
       </c>
       <c r="Z70" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA70" s="8"/>
     </row>
@@ -27910,10 +27910,10 @@
         <v>5.521188384547159</v>
       </c>
       <c r="Y72" s="20">
-        <v>11.045016882388722</v>
+        <v>10.942592571390605</v>
       </c>
       <c r="Z72" s="20">
-        <v>10.734777629887887</v>
+        <v>10.323111260338209</v>
       </c>
       <c r="AA72" s="20"/>
       <c r="AB72" s="11"/>
@@ -28055,10 +28055,10 @@
         <v>8.4147836021540883</v>
       </c>
       <c r="Y73" s="20">
-        <v>11.138055081209487</v>
+        <v>11.334046022857322</v>
       </c>
       <c r="Z73" s="20">
-        <v>12.743131105582563</v>
+        <v>12.967880780009324</v>
       </c>
       <c r="AA73" s="20"/>
       <c r="AB73" s="11"/>
@@ -28200,10 +28200,10 @@
         <v>4.3366430056793064</v>
       </c>
       <c r="Y74" s="20">
-        <v>8.048011112167714</v>
+        <v>4.6877572286336147</v>
       </c>
       <c r="Z74" s="20">
-        <v>4.4793513065383763</v>
+        <v>4.4890015272966792</v>
       </c>
       <c r="AA74" s="20"/>
       <c r="AB74" s="11"/>
@@ -28438,10 +28438,10 @@
         <v>7.2172458408579701</v>
       </c>
       <c r="Y76" s="20">
-        <v>10.927035977024445</v>
+        <v>10.81820116120052</v>
       </c>
       <c r="Z76" s="20">
-        <v>11.620795066471118</v>
+        <v>11.641468084533642</v>
       </c>
       <c r="AA76" s="20"/>
       <c r="AB76" s="11"/>
@@ -28789,7 +28789,7 @@
     </row>
     <row r="82" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -28880,7 +28880,7 @@
     </row>
     <row r="85" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -29189,10 +29189,10 @@
         <v>117.64016024571005</v>
       </c>
       <c r="Z91" s="20">
-        <v>122.5394980978698</v>
+        <v>122.58528945352197</v>
       </c>
       <c r="AA91" s="20">
-        <v>128.48681054918231</v>
+        <v>128.47293388971067</v>
       </c>
       <c r="AB91" s="11"/>
       <c r="AC91" s="11"/>
@@ -29341,10 +29341,10 @@
         <v>117.33166508097088</v>
       </c>
       <c r="Z92" s="20">
-        <v>121.07021982163148</v>
+        <v>121.07661203442299</v>
       </c>
       <c r="AA92" s="20">
-        <v>124.57762533734422</v>
+        <v>124.61619052004707</v>
       </c>
       <c r="AB92" s="11"/>
       <c r="AC92" s="11"/>
@@ -29493,10 +29493,10 @@
         <v>123.08075325116914</v>
       </c>
       <c r="Z93" s="20">
-        <v>128.2305663038612</v>
+        <v>128.21687715660346</v>
       </c>
       <c r="AA93" s="20">
-        <v>133.68095605631086</v>
+        <v>133.66961461813577</v>
       </c>
       <c r="AB93" s="11"/>
       <c r="AC93" s="11"/>
@@ -29743,10 +29743,10 @@
         <v>117.768121250984</v>
       </c>
       <c r="Z95" s="20">
-        <v>121.95486174267675</v>
+        <v>121.96063731852473</v>
       </c>
       <c r="AA95" s="20">
-        <v>126.32084348445454</v>
+        <v>126.32049892057375</v>
       </c>
       <c r="AB95" s="11"/>
       <c r="AC95" s="11"/>
@@ -30000,7 +30000,7 @@
     </row>
     <row r="102" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -30091,7 +30091,7 @@
     </row>
     <row r="105" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -30400,10 +30400,10 @@
         <v>32.352042323802621</v>
       </c>
       <c r="Z111" s="20">
-        <v>32.577104904936263</v>
+        <v>32.589652333773309</v>
       </c>
       <c r="AA111" s="20">
-        <v>32.715831696227362</v>
+        <v>32.586658375553135</v>
       </c>
       <c r="AB111" s="11"/>
       <c r="AC111" s="11"/>
@@ -30552,10 +30552,10 @@
         <v>61.530032654661994</v>
       </c>
       <c r="Z112" s="20">
-        <v>61.427558618460885</v>
+        <v>61.596655115360797</v>
       </c>
       <c r="AA112" s="20">
-        <v>61.636086193006498</v>
+        <v>61.936496562113689</v>
       </c>
       <c r="AB112" s="11"/>
       <c r="AC112" s="11"/>
@@ -30704,10 +30704,10 @@
         <v>6.1179250215353882</v>
       </c>
       <c r="Z113" s="20">
-        <v>5.9953364766028461</v>
+        <v>5.8136925508658832</v>
       </c>
       <c r="AA113" s="20">
-        <v>5.6480821107661399</v>
+        <v>5.4768450623331777</v>
       </c>
       <c r="AB113" s="11"/>
       <c r="AC113" s="11"/>
@@ -31349,7 +31349,7 @@
     </row>
     <row r="122" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -31440,7 +31440,7 @@
     </row>
     <row r="125" spans="1:96" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -31749,10 +31749,10 @@
         <v>32.387232686088538</v>
       </c>
       <c r="Z131" s="20">
-        <v>32.421679428498024</v>
+        <v>32.423586764243225</v>
       </c>
       <c r="AA131" s="20">
-        <v>32.164324396401589</v>
+        <v>32.040701644502903</v>
       </c>
       <c r="AB131" s="11"/>
       <c r="AC131" s="11"/>
@@ -31901,10 +31901,10 @@
         <v>61.758915133869138</v>
       </c>
       <c r="Z132" s="20">
-        <v>61.876400567714931</v>
+        <v>62.046395157001463</v>
       </c>
       <c r="AA132" s="20">
-        <v>62.498561646985927</v>
+        <v>62.783568607483431</v>
       </c>
       <c r="AB132" s="11"/>
       <c r="AC132" s="11"/>
@@ -32053,10 +32053,10 @@
         <v>5.8538521800423284</v>
       </c>
       <c r="Z133" s="20">
-        <v>5.701920003787043</v>
+        <v>5.5300180787552859</v>
       </c>
       <c r="AA133" s="20">
-        <v>5.3371139566124866</v>
+        <v>5.1757297480136684</v>
       </c>
       <c r="AB133" s="11"/>
       <c r="AC133" s="11"/>
